--- a/AAII_Financials/Quarterly/NVZMY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NVZMY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="92">
   <si>
     <t>NVZMY</t>
   </si>
@@ -656,86 +656,90 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
-      </c>
-      <c r="L7" s="2">
-        <v>45291</v>
       </c>
       <c r="M7" s="2">
         <v>45291</v>
       </c>
       <c r="N7" s="2">
-        <v>45107</v>
+        <v>45291</v>
       </c>
       <c r="O7" s="2">
         <v>45107</v>
       </c>
       <c r="P7" s="2">
+        <v>45107</v>
+      </c>
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -784,8 +788,11 @@
       <c r="R8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -834,8 +841,11 @@
       <c r="R9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -884,8 +894,11 @@
       <c r="R10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -904,8 +917,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -954,8 +968,11 @@
       <c r="R12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1004,8 +1021,11 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1054,8 +1074,11 @@
       <c r="R14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1104,8 +1127,11 @@
       <c r="R15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1121,8 +1147,9 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1171,8 +1198,11 @@
       <c r="R17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1221,8 +1251,11 @@
       <c r="R18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1241,8 +1274,9 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1291,8 +1325,11 @@
       <c r="R20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1341,8 +1378,11 @@
       <c r="R21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1391,8 +1431,11 @@
       <c r="R22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1441,8 +1484,11 @@
       <c r="R23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1491,8 +1537,11 @@
       <c r="R24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1541,8 +1590,11 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1591,8 +1643,11 @@
       <c r="R26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1641,8 +1696,11 @@
       <c r="R27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1691,8 +1749,11 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1741,8 +1802,11 @@
       <c r="R29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1791,8 +1855,11 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1841,8 +1908,11 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1891,8 +1961,11 @@
       <c r="R32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1941,8 +2014,11 @@
       <c r="R33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1991,8 +2067,11 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2041,63 +2120,69 @@
       <c r="R35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
-      </c>
-      <c r="L38" s="2">
-        <v>45291</v>
       </c>
       <c r="M38" s="2">
         <v>45291</v>
       </c>
       <c r="N38" s="2">
-        <v>45107</v>
+        <v>45291</v>
       </c>
       <c r="O38" s="2">
         <v>45107</v>
       </c>
       <c r="P38" s="2">
+        <v>45107</v>
+      </c>
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2116,8 +2201,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2136,58 +2222,62 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>352700</v>
+      </c>
+      <c r="E41" s="3">
         <v>377300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>323200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>330000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>385400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>269700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>289900</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K41" s="3">
+      <c r="K41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L41" s="3">
         <v>279400</v>
-      </c>
-      <c r="L41" s="3">
-        <v>165500</v>
       </c>
       <c r="M41" s="3">
         <v>165500</v>
       </c>
       <c r="N41" s="3">
-        <v>153600</v>
+        <v>165500</v>
       </c>
       <c r="O41" s="3">
         <v>153600</v>
       </c>
       <c r="P41" s="3">
+        <v>153600</v>
+      </c>
+      <c r="Q41" s="3">
         <v>160400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>149600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>181400</v>
       </c>
     </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2236,358 +2326,382 @@
       <c r="R42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1064000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1064900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1074800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1061500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1041600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1036600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>893700</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K43" s="3">
+      <c r="K43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L43" s="3">
         <v>885600</v>
-      </c>
-      <c r="L43" s="3">
-        <v>644600</v>
       </c>
       <c r="M43" s="3">
         <v>644600</v>
       </c>
       <c r="N43" s="3">
-        <v>630400</v>
+        <v>644600</v>
       </c>
       <c r="O43" s="3">
         <v>630400</v>
       </c>
       <c r="P43" s="3">
+        <v>630400</v>
+      </c>
+      <c r="Q43" s="3">
         <v>664400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>595300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>537600</v>
       </c>
     </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>955400</v>
+      </c>
+      <c r="E44" s="3">
         <v>914000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>906700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>870600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>939000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>789300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>746000</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K44" s="3">
+      <c r="K44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L44" s="3">
         <v>736500</v>
-      </c>
-      <c r="L44" s="3">
-        <v>537900</v>
       </c>
       <c r="M44" s="3">
         <v>537900</v>
       </c>
       <c r="N44" s="3">
-        <v>580700</v>
+        <v>537900</v>
       </c>
       <c r="O44" s="3">
         <v>580700</v>
       </c>
       <c r="P44" s="3">
+        <v>580700</v>
+      </c>
+      <c r="Q44" s="3">
         <v>561600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>546400</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>495000</v>
       </c>
     </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E45" s="3">
         <v>2500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>23800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>33100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>43700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>7600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>16200</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L45" s="3">
         <v>35300</v>
-      </c>
-      <c r="L45" s="3">
-        <v>55200</v>
       </c>
       <c r="M45" s="3">
         <v>55200</v>
       </c>
       <c r="N45" s="3">
-        <v>9200</v>
+        <v>55200</v>
       </c>
       <c r="O45" s="3">
         <v>9200</v>
       </c>
       <c r="P45" s="3">
+        <v>9200</v>
+      </c>
+      <c r="Q45" s="3">
         <v>12300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>11500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>14100</v>
       </c>
     </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2377700</v>
+      </c>
+      <c r="E46" s="3">
         <v>2358700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2328500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2295200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2409700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2103200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1945800</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K46" s="3">
+      <c r="K46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L46" s="3">
         <v>1936800</v>
-      </c>
-      <c r="L46" s="3">
-        <v>1403200</v>
       </c>
       <c r="M46" s="3">
         <v>1403200</v>
       </c>
       <c r="N46" s="3">
-        <v>1374000</v>
+        <v>1403200</v>
       </c>
       <c r="O46" s="3">
         <v>1374000</v>
       </c>
       <c r="P46" s="3">
+        <v>1374000</v>
+      </c>
+      <c r="Q46" s="3">
         <v>1398700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1327700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1228100</v>
       </c>
     </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>17000</v>
+      </c>
+      <c r="E47" s="3">
         <v>18700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>20500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>24200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>23700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>24500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>24800</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K47" s="3">
+      <c r="K47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L47" s="3">
         <v>27500</v>
-      </c>
-      <c r="L47" s="3">
-        <v>30400</v>
       </c>
       <c r="M47" s="3">
         <v>30400</v>
       </c>
       <c r="N47" s="3">
-        <v>32100</v>
+        <v>30400</v>
       </c>
       <c r="O47" s="3">
         <v>32100</v>
       </c>
       <c r="P47" s="3">
+        <v>32100</v>
+      </c>
+      <c r="Q47" s="3">
         <v>31800</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>32000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>29800</v>
       </c>
     </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3597600</v>
+      </c>
+      <c r="E48" s="3">
         <v>3522700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3520400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3366200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3328400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3150800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3073100</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K48" s="3">
+      <c r="K48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L48" s="3">
         <v>3071100</v>
-      </c>
-      <c r="L48" s="3">
-        <v>1827800</v>
       </c>
       <c r="M48" s="3">
         <v>1827800</v>
       </c>
       <c r="N48" s="3">
-        <v>1808000</v>
+        <v>1827800</v>
       </c>
       <c r="O48" s="3">
         <v>1808000</v>
       </c>
       <c r="P48" s="3">
+        <v>1808000</v>
+      </c>
+      <c r="Q48" s="3">
         <v>1770200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1734800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1576100</v>
       </c>
     </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>12703600</v>
+      </c>
+      <c r="E49" s="3">
         <v>12843300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>13019100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>13108900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>13161700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>10675700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>10378100</v>
       </c>
-      <c r="J49" s="3">
-        <v>0</v>
-      </c>
       <c r="K49" s="3">
+        <v>0</v>
+      </c>
+      <c r="L49" s="3">
         <v>10996800</v>
-      </c>
-      <c r="L49" s="3">
-        <v>672100</v>
       </c>
       <c r="M49" s="3">
         <v>672100</v>
       </c>
       <c r="N49" s="3">
-        <v>669000</v>
+        <v>672100</v>
       </c>
       <c r="O49" s="3">
         <v>669000</v>
       </c>
       <c r="P49" s="3">
+        <v>669000</v>
+      </c>
+      <c r="Q49" s="3">
         <v>670700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>675000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>652900</v>
       </c>
     </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2636,8 +2750,11 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2686,43 +2803,46 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>26600</v>
+      </c>
+      <c r="E52" s="3">
         <v>25800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>22900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>21600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>25800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>26200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>25600</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K52" s="3">
+      <c r="K52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L52" s="3">
         <v>37000</v>
-      </c>
-      <c r="L52" s="3">
-        <v>15600</v>
       </c>
       <c r="M52" s="3">
         <v>15600</v>
       </c>
       <c r="N52" s="3">
-        <v>17400</v>
+        <v>15600</v>
       </c>
       <c r="O52" s="3">
         <v>17400</v>
@@ -2731,13 +2851,16 @@
         <v>17400</v>
       </c>
       <c r="Q52" s="3">
+        <v>17400</v>
+      </c>
+      <c r="R52" s="3">
         <v>17800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>10800</v>
       </c>
     </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2786,58 +2909,64 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>19002600</v>
+      </c>
+      <c r="E54" s="3">
         <v>19051400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>19195800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>19127800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>19261400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>16274800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>15732100</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K54" s="3">
+      <c r="K54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L54" s="3">
         <v>16342200</v>
-      </c>
-      <c r="L54" s="3">
-        <v>4210300</v>
       </c>
       <c r="M54" s="3">
         <v>4210300</v>
       </c>
       <c r="N54" s="3">
-        <v>4137600</v>
+        <v>4210300</v>
       </c>
       <c r="O54" s="3">
         <v>4137600</v>
       </c>
       <c r="P54" s="3">
+        <v>4137600</v>
+      </c>
+      <c r="Q54" s="3">
         <v>4124800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>4020600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>3686000</v>
       </c>
     </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2856,8 +2985,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2876,308 +3006,327 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>418500</v>
+      </c>
+      <c r="E57" s="3">
         <v>419500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>494100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>349900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>354800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>343300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>438000</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K57" s="3">
+      <c r="K57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L57" s="3">
         <v>370500</v>
-      </c>
-      <c r="L57" s="3">
-        <v>239600</v>
       </c>
       <c r="M57" s="3">
         <v>239600</v>
       </c>
       <c r="N57" s="3">
-        <v>193600</v>
+        <v>239600</v>
       </c>
       <c r="O57" s="3">
         <v>193600</v>
       </c>
       <c r="P57" s="3">
+        <v>193600</v>
+      </c>
+      <c r="Q57" s="3">
         <v>211800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>268500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>239300</v>
       </c>
     </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>271100</v>
+      </c>
+      <c r="E58" s="3">
         <v>333300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1997800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>355500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>407500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>464700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>275800</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
       <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3">
         <v>982200</v>
-      </c>
-      <c r="L58" s="3">
-        <v>477500</v>
       </c>
       <c r="M58" s="3">
         <v>477500</v>
       </c>
       <c r="N58" s="3">
-        <v>480800</v>
+        <v>477500</v>
       </c>
       <c r="O58" s="3">
         <v>480800</v>
       </c>
       <c r="P58" s="3">
+        <v>480800</v>
+      </c>
+      <c r="Q58" s="3">
         <v>485300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>437100</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>377900</v>
       </c>
     </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>678300</v>
+      </c>
+      <c r="E59" s="3">
         <v>656600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>726800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>716600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>613000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>456900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>412900</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K59" s="3">
+      <c r="K59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L59" s="3">
         <v>394400</v>
-      </c>
-      <c r="L59" s="3">
-        <v>238200</v>
       </c>
       <c r="M59" s="3">
         <v>238200</v>
       </c>
       <c r="N59" s="3">
-        <v>327600</v>
+        <v>238200</v>
       </c>
       <c r="O59" s="3">
         <v>327600</v>
       </c>
       <c r="P59" s="3">
+        <v>327600</v>
+      </c>
+      <c r="Q59" s="3">
         <v>340700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>195300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>337300</v>
       </c>
     </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1367900</v>
+      </c>
+      <c r="E60" s="3">
         <v>1409400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3218600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1422000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1375300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1264800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1126700</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K60" s="3">
+      <c r="K60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L60" s="3">
         <v>1747100</v>
-      </c>
-      <c r="L60" s="3">
-        <v>1076900</v>
       </c>
       <c r="M60" s="3">
         <v>1076900</v>
       </c>
       <c r="N60" s="3">
-        <v>1002000</v>
+        <v>1076900</v>
       </c>
       <c r="O60" s="3">
         <v>1002000</v>
       </c>
       <c r="P60" s="3">
+        <v>1002000</v>
+      </c>
+      <c r="Q60" s="3">
         <v>1037800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1000400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>954500</v>
       </c>
     </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3234400</v>
+      </c>
+      <c r="E61" s="3">
         <v>3370500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1530900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3290600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>3493500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1371700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1584400</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
+        <v>0</v>
+      </c>
+      <c r="L61" s="3">
         <v>1149100</v>
-      </c>
-      <c r="L61" s="3">
-        <v>676400</v>
       </c>
       <c r="M61" s="3">
         <v>676400</v>
       </c>
       <c r="N61" s="3">
-        <v>710200</v>
+        <v>676400</v>
       </c>
       <c r="O61" s="3">
         <v>710200</v>
       </c>
       <c r="P61" s="3">
+        <v>710200</v>
+      </c>
+      <c r="Q61" s="3">
         <v>722000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>561400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>532100</v>
       </c>
     </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>88000</v>
+      </c>
+      <c r="E62" s="3">
         <v>77400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>61900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>73000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>68600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>45800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>41100</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L62" s="3">
         <v>23400</v>
-      </c>
-      <c r="L62" s="3">
-        <v>14800</v>
       </c>
       <c r="M62" s="3">
         <v>14800</v>
       </c>
       <c r="N62" s="3">
-        <v>133100</v>
+        <v>14800</v>
       </c>
       <c r="O62" s="3">
         <v>133100</v>
       </c>
       <c r="P62" s="3">
+        <v>133100</v>
+      </c>
+      <c r="Q62" s="3">
         <v>162200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>158500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>159400</v>
       </c>
     </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3226,8 +3375,11 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3276,8 +3428,11 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3326,58 +3481,64 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>6258500</v>
+      </c>
+      <c r="E66" s="3">
         <v>6461100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>6450500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>6521800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>6645000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4136100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4161500</v>
       </c>
-      <c r="J66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K66" s="3">
+      <c r="K66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L66" s="3">
         <v>4550700</v>
-      </c>
-      <c r="L66" s="3">
-        <v>2082100</v>
       </c>
       <c r="M66" s="3">
         <v>2082100</v>
       </c>
       <c r="N66" s="3">
-        <v>2115000</v>
+        <v>2082100</v>
       </c>
       <c r="O66" s="3">
         <v>2115000</v>
       </c>
       <c r="P66" s="3">
+        <v>2115000</v>
+      </c>
+      <c r="Q66" s="3">
         <v>2187300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1976300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1835700</v>
       </c>
     </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3396,8 +3557,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3446,8 +3608,11 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3496,8 +3661,11 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3546,8 +3714,11 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3596,58 +3767,64 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>12878400</v>
+      </c>
+      <c r="E72" s="3">
         <v>12788300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>13101400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>12951700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>12961500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>12110100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>11421900</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K72" s="3">
+      <c r="K72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L72" s="3">
         <v>11678700</v>
-      </c>
-      <c r="L72" s="3">
-        <v>2039800</v>
       </c>
       <c r="M72" s="3">
         <v>2039800</v>
       </c>
       <c r="N72" s="3">
-        <v>1890900</v>
+        <v>2039800</v>
       </c>
       <c r="O72" s="3">
         <v>1890900</v>
       </c>
       <c r="P72" s="3">
+        <v>1890900</v>
+      </c>
+      <c r="Q72" s="3">
         <v>1791200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>1876700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>1582200</v>
       </c>
     </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3696,8 +3873,11 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3746,8 +3926,11 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3796,58 +3979,64 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>12744100</v>
+      </c>
+      <c r="E76" s="3">
         <v>12590300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>12745300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>12606000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>12616400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>12138700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>11570600</v>
       </c>
-      <c r="J76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K76" s="3">
+      <c r="K76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L76" s="3">
         <v>11789900</v>
-      </c>
-      <c r="L76" s="3">
-        <v>2072900</v>
       </c>
       <c r="M76" s="3">
         <v>2072900</v>
       </c>
       <c r="N76" s="3">
-        <v>1962100</v>
+        <v>2072900</v>
       </c>
       <c r="O76" s="3">
         <v>1962100</v>
       </c>
       <c r="P76" s="3">
+        <v>1962100</v>
+      </c>
+      <c r="Q76" s="3">
         <v>1878200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1988100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1799300</v>
       </c>
     </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3896,63 +4085,69 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
-      </c>
-      <c r="L80" s="2">
-        <v>45291</v>
       </c>
       <c r="M80" s="2">
         <v>45291</v>
       </c>
       <c r="N80" s="2">
-        <v>45107</v>
+        <v>45291</v>
       </c>
       <c r="O80" s="2">
         <v>45107</v>
       </c>
       <c r="P80" s="2">
+        <v>45107</v>
+      </c>
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -4001,8 +4196,11 @@
       <c r="R81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4021,58 +4219,62 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>71900</v>
+      </c>
+      <c r="E83" s="3">
         <v>69500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>68200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>66900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>64400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>68300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>9600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>47100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>25700</v>
-      </c>
-      <c r="L83" s="3">
-        <v>154900</v>
       </c>
       <c r="M83" s="3">
         <v>154900</v>
       </c>
       <c r="N83" s="3">
-        <v>53000</v>
+        <v>154900</v>
       </c>
       <c r="O83" s="3">
         <v>53000</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q83" s="3">
+      <c r="P83" s="3">
+        <v>53000</v>
+      </c>
+      <c r="Q83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R83" s="3">
         <v>158500</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4121,8 +4323,11 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4171,8 +4376,11 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4221,8 +4429,11 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4271,8 +4482,11 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4321,58 +4535,64 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>406900</v>
+      </c>
+      <c r="E89" s="3">
         <v>192700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>385300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>547700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>375900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>115000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>237300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>292900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>376700</v>
-      </c>
-      <c r="L89" s="3">
-        <v>166400</v>
       </c>
       <c r="M89" s="3">
         <v>166400</v>
       </c>
       <c r="N89" s="3">
-        <v>165700</v>
+        <v>166400</v>
       </c>
       <c r="O89" s="3">
         <v>165700</v>
       </c>
       <c r="P89" s="3">
+        <v>165700</v>
+      </c>
+      <c r="Q89" s="3">
         <v>45800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>83900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>160700</v>
       </c>
     </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4391,58 +4611,62 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-112500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-91200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-230700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-111800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-85300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-49100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-131300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-85100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-96100</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-72400</v>
       </c>
       <c r="M91" s="3">
         <v>-72400</v>
       </c>
       <c r="N91" s="3">
-        <v>-75400</v>
+        <v>-72400</v>
       </c>
       <c r="O91" s="3">
         <v>-75400</v>
       </c>
       <c r="P91" s="3">
+        <v>-75400</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-60500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-119300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-97100</v>
       </c>
     </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4491,8 +4715,11 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4541,58 +4768,64 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-198900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-107300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-265600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-193600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1810200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-41400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-101700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-52000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-26100</v>
-      </c>
-      <c r="L94" s="3">
-        <v>-89400</v>
       </c>
       <c r="M94" s="3">
         <v>-89400</v>
       </c>
       <c r="N94" s="3">
-        <v>-103300</v>
+        <v>-89400</v>
       </c>
       <c r="O94" s="3">
         <v>-103300</v>
       </c>
       <c r="P94" s="3">
+        <v>-103300</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-49400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-129000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-61100</v>
       </c>
     </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4611,58 +4844,62 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
+      <c r="D96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E96" s="3">
         <v>305700</v>
       </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
       <c r="F96" s="3">
+        <v>0</v>
+      </c>
+      <c r="G96" s="3">
         <v>164600</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>308200</v>
       </c>
-      <c r="H96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
+      <c r="I96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
         <v>139300</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>133800</v>
-      </c>
-      <c r="L96" s="3">
-        <v>172500</v>
       </c>
       <c r="M96" s="3">
         <v>172500</v>
       </c>
       <c r="N96" s="3">
-        <v>100</v>
+        <v>172500</v>
       </c>
       <c r="O96" s="3">
         <v>100</v>
       </c>
       <c r="P96" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q96" s="3">
         <v>242400</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
-      <c r="R96" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4711,8 +4948,11 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4761,8 +5001,11 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4811,154 +5054,166 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-235600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-29900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-119900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-412900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1537800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-110400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-125100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-233100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-303800</v>
-      </c>
-      <c r="L100" s="3">
-        <v>-82300</v>
       </c>
       <c r="M100" s="3">
         <v>-82300</v>
       </c>
       <c r="N100" s="3">
-        <v>-66800</v>
+        <v>-82300</v>
       </c>
       <c r="O100" s="3">
         <v>-66800</v>
       </c>
       <c r="P100" s="3">
+        <v>-66800</v>
+      </c>
+      <c r="Q100" s="3">
         <v>14400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>3300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-54500</v>
       </c>
     </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="E101" s="3">
         <v>3800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-3400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>5900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>4600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>7600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-3400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-3200</v>
-      </c>
-      <c r="L101" s="3">
-        <v>-6500</v>
       </c>
       <c r="M101" s="3">
         <v>-6500</v>
       </c>
       <c r="N101" s="3">
-        <v>3100</v>
+        <v>-6500</v>
       </c>
       <c r="O101" s="3">
         <v>3100</v>
       </c>
       <c r="P101" s="3">
+        <v>3100</v>
+      </c>
+      <c r="Q101" s="3">
         <v>-700</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>9300</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-21100</v>
+      </c>
+      <c r="E102" s="3">
         <v>59800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-7000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-55000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>92400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-33000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>7100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>13700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>51400</v>
-      </c>
-      <c r="L102" s="3">
-        <v>-8700</v>
       </c>
       <c r="M102" s="3">
         <v>-8700</v>
       </c>
       <c r="N102" s="3">
-        <v>-7600</v>
+        <v>-8700</v>
       </c>
       <c r="O102" s="3">
         <v>-7600</v>
       </c>
       <c r="P102" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="Q102" s="3">
         <v>8600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-48300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>48000</v>
       </c>
     </row>
